--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120182288</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129362707</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104331</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220461</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>300 m S Bokeslund, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>413302</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6201506</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>fuktig skogsstig</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104331</v>
+        <v>104347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104347</v>
+        <v>104349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104349</v>
+        <v>104350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104350</v>
+        <v>104354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104354</v>
+        <v>104356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104356</v>
+        <v>104360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104360</v>
+        <v>104370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104370</v>
+        <v>104373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104373</v>
+        <v>104402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104402</v>
+        <v>104414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104414</v>
+        <v>104415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>129362707</v>
       </c>
       <c r="B3" t="n">
-        <v>104415</v>
+        <v>104420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120182288</v>
+        <v>129362707</v>
       </c>
       <c r="B2" t="n">
-        <v>96885</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tullskog, Tullskog, Sk</t>
+          <t>300 m S Bokeslund, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412817</v>
+        <v>413302</v>
       </c>
       <c r="R2" t="n">
-        <v>6201843</v>
+        <v>6201506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,25 +757,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>fuktig skogsstig</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jacob Björnberg</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jacob Björnberg</t>
+          <t>Torbjörn Tyler</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129362707</v>
+        <v>120182288</v>
       </c>
       <c r="B3" t="n">
-        <v>104420</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +788,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220461</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>With.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>300 m S Bokeslund, Sk</t>
+          <t>Tullskog, Tullskog, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413302</v>
+        <v>412817</v>
       </c>
       <c r="R3" t="n">
-        <v>6201506</v>
+        <v>6201843</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,20 +878,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>fuktig skogsstig</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Torbjörn Tyler</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Torbjörn Tyler</t>
+          <t>Jacob Björnberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 2942-2024 artfynd.xlsx
+++ b/artfynd/A 2942-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129362707</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120182288</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>